--- a/HyperAutomation/resources/Status_SAC.xlsx
+++ b/HyperAutomation/resources/Status_SAC.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,17 +40,11 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00166534"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00991B1B"/>
+      <color rgb="0092400E"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -64,12 +58,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
+        <fgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
   </fills>
@@ -99,14 +88,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -548,12 +536,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>#SAC-2026-3135</t>
+          <t>#SAC-2026-1653</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>23/08/2026 22:11:27</t>
+          <t>24/08/2026 11:01:59</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -578,39 +566,39 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>SUCESSO</t>
+          <t>DUPLICADO</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>CONFIRMACAO_ENVIADA</t>
+          <t>NOTIFICACAO_ERRO_ENVIADA</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Cadastro realizado com sucesso</t>
+          <t>Cadastro duplicado: CPF já existente na base de dados do Portal Fake</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Enviado com sucesso</t>
+          <t>Não enviado (Opção desativada)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>23/08/2026 22:11:31</t>
+          <t>24/08/2026 11:01:59</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>#SAC-2026-8809</t>
+          <t>#SAC-2026-4292</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>23/08/2026 22:11:27</t>
+          <t>24/08/2026 11:01:59</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -635,44 +623,44 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>SUCESSO</t>
+          <t>DUPLICADO</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>CONFIRMACAO_ENVIADA</t>
+          <t>NOTIFICACAO_ERRO_ENVIADA</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Cadastro realizado com sucesso</t>
+          <t>Cadastro duplicado: CPF já existente na base de dados do Portal Fake</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Enviado com sucesso</t>
+          <t>Não enviado (Opção desativada)</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>23/08/2026 22:11:35</t>
+          <t>24/08/2026 11:01:59</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>#SAC-2026-8816</t>
+          <t>#SAC-2026-2122</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>23/08/2026 22:11:27</t>
+          <t>24/08/2026 11:01:59</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Fani</t>
+          <t>Fani Batista</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -692,39 +680,39 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>ERRO_CADASTRO</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
+          <t>DUPLICADO</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>NOTIFICACAO_ERRO_ENVIADA</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Erro no preenchimento/validação do formulário: Erro na validação do formulário</t>
+          <t>Cadastro duplicado: CPF já existente na base de dados do Portal Fake</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Enviado com sucesso</t>
+          <t>Não enviado (Opção desativada)</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>23/08/2026 22:11:38</t>
+          <t>24/08/2026 11:01:59</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>#SAC-2026-5467</t>
+          <t>#SAC-2026-6072</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>23/08/2026 22:11:27</t>
+          <t>24/08/2026 11:01:59</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -749,27 +737,27 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>SUCESSO</t>
+          <t>DUPLICADO</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>CONFIRMACAO_ENVIADA</t>
+          <t>NOTIFICACAO_ERRO_ENVIADA</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Cadastro realizado com sucesso</t>
+          <t>Cadastro duplicado: CPF já existente na base de dados do Portal Fake</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Enviado com sucesso</t>
+          <t>Não enviado (Opção desativada)</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23/08/2026 22:11:42</t>
+          <t>24/08/2026 11:01:59</t>
         </is>
       </c>
     </row>

--- a/HyperAutomation/resources/Status_SAC.xlsx
+++ b/HyperAutomation/resources/Status_SAC.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status SAC" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Status SAC'!$A$1:$K$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Status SAC'!$A$1:$K$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -40,7 +40,7 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="0092400E"/>
+      <color rgb="00166534"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -58,7 +58,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
+        <fgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
   </fills>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -536,233 +536,62 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>#SAC-2026-1653</t>
+          <t>#SAC-2026-7378</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026 11:01:59</t>
+          <t>24/08/2026 17:41:46</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>João Pedro Almeida</t>
+          <t>Sannyer Nery</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>12345678909</t>
+          <t>035.360.542-50</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>joao.almeida.teste@example.com</t>
+          <t>portalfakeifam@gmail.com</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>(11) 98765-4321</t>
+          <t>(92) 99982-7524</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>DUPLICADO</t>
+          <t>SUCESSO</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>NOTIFICACAO_ERRO_ENVIADA</t>
+          <t>CONFIRMACAO_ENVIADA</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Cadastro duplicado: CPF já existente na base de dados do Portal Fake</t>
+          <t>Cadastro realizado com sucesso</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Não enviado (Opção desativada)</t>
+          <t>Enviado com sucesso</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026 11:01:59</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>#SAC-2026-4292</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/08/2026 11:01:59</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Mariana Costa Ribeiro</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>98765432100</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>mariana.ribeiro.teste@example.com</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>(21) 99876-1234</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>DUPLICADO</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>NOTIFICACAO_ERRO_ENVIADA</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Cadastro duplicado: CPF já existente na base de dados do Portal Fake</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Não enviado (Opção desativada)</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>24/08/2026 11:01:59</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>#SAC-2026-2122</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>24/08/2026 11:01:59</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Fani Batista</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>02033414221</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>fani.souza19@gmail.com</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>(92) 99503-7524</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>DUPLICADO</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>NOTIFICACAO_ERRO_ENVIADA</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Cadastro duplicado: CPF já existente na base de dados do Portal Fake</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Não enviado (Opção desativada)</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>24/08/2026 11:01:59</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>#SAC-2026-6072</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>24/08/2026 11:01:59</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Lucas Henrique Lima</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>11144477735</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>lucas.lima@exemplo.com</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>(92) 99123-4567</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>DUPLICADO</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>NOTIFICACAO_ERRO_ENVIADA</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Cadastro duplicado: CPF já existente na base de dados do Portal Fake</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Não enviado (Opção desativada)</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24/08/2026 11:01:59</t>
+          <t>24/08/2026 17:41:52</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K5"/>
+  <autoFilter ref="A1:K2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/HyperAutomation/resources/Status_SAC.xlsx
+++ b/HyperAutomation/resources/Status_SAC.xlsx
@@ -40,7 +40,7 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="0092400E"/>
+      <color rgb="00166534"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -58,7 +58,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
+        <fgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
   </fills>
@@ -536,12 +536,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>#SAC-2026-1653</t>
+          <t>#SAC-2026-7466</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026 11:01:59</t>
+          <t>24/08/2026 11:11:25</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -566,17 +566,17 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>DUPLICADO</t>
+          <t>SUCESSO</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>NOTIFICACAO_ERRO_ENVIADA</t>
+          <t>CONFIRMACAO_ENVIADA</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Cadastro duplicado: CPF já existente na base de dados do Portal Fake</t>
+          <t>Cadastro realizado com sucesso</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -586,19 +586,19 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026 11:01:59</t>
+          <t>24/08/2026 11:11:25</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>#SAC-2026-4292</t>
+          <t>#SAC-2026-3585</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026 11:01:59</t>
+          <t>24/08/2026 11:11:25</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -623,17 +623,17 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>DUPLICADO</t>
+          <t>SUCESSO</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>NOTIFICACAO_ERRO_ENVIADA</t>
+          <t>CONFIRMACAO_ENVIADA</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Cadastro duplicado: CPF já existente na base de dados do Portal Fake</t>
+          <t>Cadastro realizado com sucesso</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -643,19 +643,19 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026 11:01:59</t>
+          <t>24/08/2026 11:11:25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>#SAC-2026-2122</t>
+          <t>#SAC-2026-2116</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026 11:01:59</t>
+          <t>24/08/2026 11:11:25</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -680,17 +680,17 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>DUPLICADO</t>
+          <t>SUCESSO</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>NOTIFICACAO_ERRO_ENVIADA</t>
+          <t>CONFIRMACAO_ENVIADA</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Cadastro duplicado: CPF já existente na base de dados do Portal Fake</t>
+          <t>Cadastro realizado com sucesso</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -700,19 +700,19 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026 11:01:59</t>
+          <t>24/08/2026 11:11:25</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>#SAC-2026-6072</t>
+          <t>#SAC-2026-5161</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026 11:01:59</t>
+          <t>24/08/2026 11:11:25</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -737,17 +737,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>DUPLICADO</t>
+          <t>SUCESSO</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>NOTIFICACAO_ERRO_ENVIADA</t>
+          <t>CONFIRMACAO_ENVIADA</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Cadastro duplicado: CPF já existente na base de dados do Portal Fake</t>
+          <t>Cadastro realizado com sucesso</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026 11:01:59</t>
+          <t>24/08/2026 11:11:25</t>
         </is>
       </c>
     </row>

--- a/HyperAutomation/resources/Status_SAC.xlsx
+++ b/HyperAutomation/resources/Status_SAC.xlsx
@@ -536,32 +536,32 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>#SAC-2026-7378</t>
+          <t>#SAC-2026-8414</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026 17:41:46</t>
+          <t>24/08/2026 22:16:22</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Sannyer Nery</t>
+          <t>Fani Batista</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>035.360.542-50</t>
+          <t>02033414221</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>portalfakeifam@gmail.com</t>
+          <t>fani.souza19@gmail.com</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>(92) 99982-7524</t>
+          <t>(92) 99503-7524</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>24/08/2026 17:41:52</t>
+          <t>24/08/2026 22:16:25</t>
         </is>
       </c>
     </row>

--- a/HyperAutomation/resources/Status_SAC.xlsx
+++ b/HyperAutomation/resources/Status_SAC.xlsx
@@ -1,64 +1,107 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\empresa_portal_fake\HyperAutomation\resources\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C4C98A-CC49-4235-A650-7C88B3768E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status SAC" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Status SAC" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Status SAC'!$A$1:$K$2</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+  <si>
+    <t>Protocolo SAC</t>
+  </si>
+  <si>
+    <t>Data Registro</t>
+  </si>
+  <si>
+    <t>Nome Cliente</t>
+  </si>
+  <si>
+    <t>CPF</t>
+  </si>
+  <si>
+    <t>E-mail</t>
+  </si>
+  <si>
+    <t>Telefone</t>
+  </si>
+  <si>
+    <t>Status Cadastro</t>
+  </si>
+  <si>
+    <t>Status SAC</t>
+  </si>
+  <si>
+    <t>Motivo Erro / Observação</t>
+  </si>
+  <si>
+    <t>E-mail Enviado</t>
+  </si>
+  <si>
+    <t>Atualizado em</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Segoe UI"/>
-      <sz val="10"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF166534"/>
       <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00166534"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E3A8A"/>
+        <fgColor rgb="FF1E3A8A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
+        <fgColor rgb="FFDCFCE7"/>
       </patternFill>
     </fill>
   </fills>
@@ -72,102 +115,44 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="FFCBD5E1"/>
       </left>
       <right style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="FFCBD5E1"/>
       </right>
       <top style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="FFCBD5E1"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="FFCBD5E1"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -455,143 +440,72 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col min="1" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="28" customWidth="1"/>
+    <col min="9" max="9" width="45" customWidth="1"/>
+    <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="11" max="11" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Protocolo SAC</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Data Registro</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Nome Cliente</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>CPF</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>E-mail</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Telefone</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Status Cadastro</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Status SAC</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Motivo Erro / Observação</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>E-mail Enviado</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Atualizado em</t>
-        </is>
+    <row r="1" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>#SAC-2026-8414</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>24/08/2026 22:16:22</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Fani Batista</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>02033414221</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>fani.souza19@gmail.com</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>(92) 99503-7524</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>SUCESSO</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>CONFIRMACAO_ENVIADA</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Cadastro realizado com sucesso</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Enviado com sucesso</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>24/08/2026 22:16:25</t>
-        </is>
-      </c>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>